--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_261_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_261_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1356</v>
+        <v>6.2075</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9344</v>
+        <v>5.8046</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2013</v>
+        <v>0.4029</v>
       </c>
       <c r="G2" t="n">
         <v>2.7871</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7959</v>
+        <v>-1.724</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4753</v>
+        <v>-0.6051</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3205</v>
+        <v>-1.1189</v>
       </c>
       <c r="V2" t="n">
         <v>3.7527</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8192</v>
+        <v>4.6511</v>
       </c>
       <c r="E3" t="n">
         <v>4.1975</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6217</v>
+        <v>0.4536</v>
       </c>
       <c r="G3" t="n">
         <v>3.8677</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0057</v>
+        <v>-0.1623</v>
       </c>
       <c r="T3" t="n">
         <v>0.3541</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3484</v>
+        <v>-0.5164</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6778999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3701</v>
+        <v>4.4699</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0527</v>
+        <v>3.9844</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3174</v>
+        <v>0.4855</v>
       </c>
       <c r="G4" t="n">
         <v>3.0728</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1486</v>
+        <v>-1.0488</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2538</v>
+        <v>-0.322</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8948</v>
+        <v>-0.7268</v>
       </c>
       <c r="V4" t="n">
         <v>1.7501</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9869</v>
+        <v>1.465</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4137</v>
+        <v>2.0598</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4268</v>
+        <v>-0.5948</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2049</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.2034</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9164</v>
+        <v>0.5625</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1911</v>
+        <v>-0.3591</v>
       </c>
       <c r="V5" t="n">
         <v>1.4665</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7375</v>
+        <v>0.6531</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.3855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.234</v>
+        <v>0.2676</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6766</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2544</v>
+        <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3541</v>
+        <v>0.2361</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0997</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. AVRAMOVIC</t>
+          <t>N. DANGUBIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.24</v>
+        <v>0.3509</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3863</v>
+        <v>-0.3977</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1464</v>
+        <v>0.7486</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0954</v>
+        <v>0.1829</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0793</v>
+        <v>0.1861</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1746</v>
+        <v>-0.0033</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7817</v>
+        <v>0.0504</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0033</v>
+        <v>0.0504</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2216</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.877</v>
+        <v>0.1324</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.924</v>
+        <v>0.1357</v>
       </c>
       <c r="O7" t="n">
-        <v>0.047</v>
+        <v>-0.0033</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2478</v>
+        <v>-0.7598</v>
       </c>
       <c r="T7" t="n">
-        <v>0.999</v>
+        <v>-0.4481</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7512</v>
+        <v>-0.3117</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. DANGUBIC</t>
+          <t>A. AVRAMOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1605</v>
+        <v>0.0041</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6217</v>
+        <v>1.1504</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7822</v>
+        <v>-1.1464</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1829</v>
+        <v>-1.0954</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1861</v>
+        <v>0.0793</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0033</v>
+        <v>-1.1746</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0504</v>
+        <v>0.7817</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0504</v>
+        <v>2.0033</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.2216</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1324</v>
+        <v>-1.877</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1357</v>
+        <v>-1.924</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0033</v>
+        <v>0.047</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9502</v>
+        <v>0.0119</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>0.7631</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2781</v>
+        <v>-0.7512</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6038</v>
+        <v>-3.1781</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.0576</v>
+        <v>-4.8335</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4538</v>
+        <v>1.6554</v>
       </c>
       <c r="G9" t="n">
         <v>-4.2824</v>
@@ -1156,13 +1156,13 @@
         <v>2.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.788</v>
+        <v>-1.3623</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5421</v>
+        <v>-0.3181</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2458</v>
+        <v>-1.0442</v>
       </c>
       <c r="V9" t="n">
         <v>2.0026</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8623</v>
+        <v>-6.5197</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.0662</v>
+        <v>-5.4883</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7962</v>
+        <v>-1.0314</v>
       </c>
       <c r="G10" t="n">
         <v>-4.7052</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1751</v>
+        <v>-0.8325</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1123</v>
+        <v>-0.5344</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.2981</v>
       </c>
       <c r="V10" t="n">
         <v>-1.214</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.983700000000002</v>
+        <v>8.103799999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>5.742600000000001</v>
+        <v>6.862699999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.240999999999999</v>
+        <v>1.241</v>
       </c>
       <c r="G11" t="n">
         <v>-1.053999999999998</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.077299999999999</v>
+        <v>-7.077300000000001</v>
       </c>
       <c r="I11" t="n">
         <v>6.0232</v>
@@ -1312,13 +1312,13 @@
         <v>15.077</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.624600000000001</v>
+        <v>-5.5044</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.432</v>
+        <v>-0.3119</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.1924</v>
+        <v>-5.1925</v>
       </c>
       <c r="V11" t="n">
         <v>6.543899999999999</v>
@@ -1327,7 +1327,7 @@
         <v>10.7531</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.209199999999999</v>
+        <v>-4.2092</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.7831</v>
+        <v>5.7501</v>
       </c>
       <c r="E12" t="n">
-        <v>5.4284</v>
+        <v>4.2489</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3548</v>
+        <v>1.5013</v>
       </c>
       <c r="G12" t="n">
         <v>5.6711</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3672</v>
+        <v>2.3342</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3318</v>
+        <v>1.1523</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0354</v>
+        <v>1.1819</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2551</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.378</v>
+        <v>2.7527</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8723</v>
+        <v>1.7666</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2503</v>
+        <v>0.9861</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8176</v>
+        <v>4.549</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1538</v>
+        <v>1.6818</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.9714</v>
+        <v>2.8673</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1111</v>
+        <v>3.2662</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1715</v>
+        <v>0.8675</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.2827</v>
+        <v>2.3987</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2936</v>
+        <v>1.2828</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9823</v>
+        <v>0.8142</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3113</v>
+        <v>0.4685</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R13" t="n">
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1776</v>
+        <v>1.201</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4708</v>
+        <v>0.0672</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7068</v>
+        <v>1.1338</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1418</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3259</v>
+        <v>2.4383</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5871</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7387</v>
+        <v>1.9287</v>
       </c>
       <c r="G14" t="n">
-        <v>4.549</v>
+        <v>1.9458</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6818</v>
+        <v>1.3771</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8673</v>
+        <v>0.5688</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2662</v>
+        <v>1.4921</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8675</v>
+        <v>0.7093</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3987</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2828</v>
+        <v>0.4537</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8142</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4685</v>
+        <v>-0.214</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.3195</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2258</v>
+        <v>0.9564</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1123</v>
+        <v>0.4092</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8865</v>
+        <v>0.5472</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6582</v>
+        <v>1.1199</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-2.3441</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4461</v>
+        <v>3.464</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9458</v>
+        <v>-1.8176</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3771</v>
+        <v>1.1538</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5688</v>
+        <v>-2.9714</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4921</v>
+        <v>-3.1111</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7093</v>
+        <v>0.1715</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7828000000000001</v>
+        <v>-3.2827</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4537</v>
+        <v>1.2936</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.9823</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.214</v>
+        <v>0.3113</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8237</v>
+        <v>1.9195</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8883</v>
+        <v>0.999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0646</v>
+        <v>0.9206</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.798</v>
+        <v>-1.3729</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6423</v>
+        <v>0.0954</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4402</v>
+        <v>-1.4683</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1311</v>
+        <v>-2.2052</v>
       </c>
       <c r="H16" t="n">
-        <v>0.605</v>
+        <v>0.7359</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7361</v>
+        <v>-2.9411</v>
       </c>
       <c r="J16" t="n">
-        <v>0.773</v>
+        <v>-0.3929</v>
       </c>
       <c r="K16" t="n">
-        <v>0.773</v>
+        <v>1.9662</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-2.359</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9041</v>
+        <v>-1.8123</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.168</v>
+        <v>-1.2303</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7361</v>
+        <v>-0.5821</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4233</v>
+        <v>0.1544</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4233</v>
+        <v>0.2047</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.0503</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9304</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3943</v>
+        <v>0.2836</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9575</v>
+        <v>-1.4714</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5672</v>
+        <v>-4.0395</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5248</v>
+        <v>2.5681</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2052</v>
+        <v>2.0402</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7359</v>
+        <v>1.2642</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.9411</v>
+        <v>0.776</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3929</v>
+        <v>0.4537</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9662</v>
+        <v>0.4607</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.359</v>
+        <v>-0.007</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8123</v>
+        <v>1.5865</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2303</v>
+        <v>0.8035</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5821</v>
+        <v>0.7831</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-4.871</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5698</v>
+        <v>1.0398</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6765</v>
+        <v>0.3778</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1067</v>
+        <v>0.662</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5455</v>
+        <v>-1.6236</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2966</v>
+        <v>-0.1834</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.249</v>
+        <v>-1.4402</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.753</v>
+        <v>-0.1311</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2616</v>
+        <v>0.605</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5086000000000001</v>
+        <v>-0.7361</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0.773</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7359</v>
+        <v>0.773</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0539</v>
+        <v>-0.9041</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.168</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4718</v>
+        <v>-0.7361</v>
       </c>
       <c r="P18" t="n">
         <v>-1.1598</v>
@@ -1858,28 +1858,28 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3673</v>
+        <v>0.5977</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5623</v>
+        <v>0.5977</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.195</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8606</v>
+        <v>-1.7929</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0552</v>
+        <v>-1.7684</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.9158</v>
+        <v>-0.0245</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4204</v>
+        <v>-0.753</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1284</v>
+        <v>-1.2616</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.292</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5545</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9446</v>
+        <v>-0.7359</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4991</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8659</v>
+        <v>-0.0539</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.073</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7929</v>
+        <v>0.4718</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>0.1199</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5375</v>
+        <v>0.0905</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1375</v>
+        <v>0.0294</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.351</v>
+        <v>-1.9242</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6182</v>
+        <v>-0.3823</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7328</v>
+        <v>-1.5419</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4431</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7481</v>
+        <v>-0.3213</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4494</v>
+        <v>-0.2585</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0282</v>
+        <v>-2.7251</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6126</v>
+        <v>-0.3767</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4156</v>
+        <v>-2.3484</v>
       </c>
       <c r="G21" t="n">
         <v>-3.166</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4419</v>
+        <v>0.7451</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2636</v>
+        <v>0.4995</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1784</v>
+        <v>0.2456</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5361</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1851</v>
+        <v>-2.7642</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.415</v>
+        <v>1.2296</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7701</v>
+        <v>-3.9938</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2158</v>
+        <v>-2.4204</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.898</v>
+        <v>-0.1284</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3178</v>
+        <v>-2.292</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6785</v>
+        <v>-0.5545</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6785</v>
+        <v>0.9446</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.4991</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5373</v>
+        <v>-1.8659</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2195</v>
+        <v>-1.073</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3178</v>
+        <v>-0.7929</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4332</v>
+        <v>0.4964</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2636</v>
+        <v>0.7119</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6967</v>
+        <v>-0.2155</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.403</v>
+        <v>-3.0113</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4549</v>
+        <v>-0.5329</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0519</v>
+        <v>-2.4784</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0402</v>
+        <v>-2.2158</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2642</v>
+        <v>-1.898</v>
       </c>
       <c r="I23" t="n">
-        <v>0.776</v>
+        <v>-0.3178</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4537</v>
+        <v>-0.6785</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4607</v>
+        <v>-0.6785</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5865</v>
+        <v>-1.5373</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8035</v>
+        <v>-1.2195</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7831</v>
+        <v>-0.3178</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.871</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8918</v>
+        <v>-0.2594</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0376</v>
+        <v>0.1456</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1459</v>
+        <v>-0.405</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.983700000000001</v>
+        <v>-4.624599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7772</v>
+        <v>-1.777200000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.206499999999998</v>
+        <v>-2.8473</v>
       </c>
       <c r="G24" t="n">
         <v>1.053899999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>7.0773</v>
+        <v>7.077299999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-6.023199999999999</v>
@@ -2308,16 +2308,16 @@
         <v>-3.8828</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.380300000000001</v>
+        <v>-3.3803</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.239799999999999</v>
+        <v>-1.2398</v>
       </c>
       <c r="O24" t="n">
         <v>-2.1405</v>
       </c>
       <c r="P24" t="n">
-        <v>-8.1183</v>
+        <v>-8.118300000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-15.077</v>
@@ -2326,16 +2326,16 @@
         <v>6.958600000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>6.624500000000001</v>
+        <v>8.983700000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>5.1925</v>
+        <v>5.1926</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4323</v>
+        <v>3.7912</v>
       </c>
       <c r="V24" t="n">
-        <v>-6.543900000000001</v>
+        <v>-6.5439</v>
       </c>
       <c r="W24" t="n">
         <v>3.6731</v>
